--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486524_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486524_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5953</v>
+        <v>4.6949</v>
       </c>
       <c r="E2" t="n">
-        <v>0.457</v>
+        <v>1.5565</v>
       </c>
       <c r="F2" t="n">
         <v>3.1384</v>
@@ -610,10 +610,10 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6151</v>
+        <v>-0.5155</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3459</v>
+        <v>-0.2463</v>
       </c>
       <c r="U2" t="n">
         <v>-0.2692</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3485</v>
+        <v>3.3043</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6324</v>
+        <v>1.4341</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7161</v>
+        <v>1.8702</v>
       </c>
       <c r="G3" t="n">
         <v>3.064</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8238</v>
+        <v>-0.8679</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06370000000000001</v>
+        <v>-0.1346</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8875</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.0207</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4578</v>
+        <v>1.1414</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5118</v>
+        <v>-1.1385</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.054</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1468</v>
+        <v>0.8228</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0313</v>
+        <v>0.1885</v>
       </c>
       <c r="I4" t="n">
+        <v>0.6343</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1112</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7116</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.1155</v>
       </c>
-      <c r="J4" t="n">
-        <v>1.7439</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.3996</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.3442</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-0.597</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-0.3683</v>
-      </c>
       <c r="O4" t="n">
-        <v>-0.2287</v>
+        <v>0.596</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3926</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3926</v>
+        <v>0.435</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1577</v>
+        <v>0.2316</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8773</v>
+        <v>-0.1622</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7196</v>
+        <v>0.3939</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2393</v>
+        <v>0.7395</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.1093</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.209</v>
+        <v>0.9298</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9764</v>
+        <v>1.6664</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7674</v>
+        <v>-0.7366</v>
       </c>
       <c r="G5" t="n">
         <v>1.6439</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8702</v>
+        <v>0.5909</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6922</v>
+        <v>0.3822</v>
       </c>
       <c r="U5" t="n">
-        <v>0.178</v>
+        <v>0.2088</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9989</v>
+        <v>0.8741</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2503</v>
+        <v>0.8665</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2491</v>
+        <v>0.0076</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8228</v>
+        <v>1.1468</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1885</v>
+        <v>1.0313</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6343</v>
+        <v>0.1155</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1112</v>
+        <v>1.7439</v>
       </c>
       <c r="K6" t="n">
-        <v>0.073</v>
+        <v>1.3996</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0382</v>
+        <v>0.3442</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7116</v>
+        <v>-0.597</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1155</v>
+        <v>-0.3683</v>
       </c>
       <c r="O6" t="n">
-        <v>0.596</v>
+        <v>-0.2287</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.435</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.089</v>
+        <v>-0.426</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.274</v>
+        <v>0.2319</v>
       </c>
       <c r="U6" t="n">
-        <v>0.363</v>
+        <v>-0.6579</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7395</v>
+        <v>-2.2393</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-1.1093</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9821</v>
+        <v>-0.899</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5974</v>
+        <v>-1.2369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.338</v>
       </c>
       <c r="G7" t="n">
         <v>2.6834</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0586</v>
+        <v>-0.9755</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0154</v>
+        <v>-0.6549</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0432</v>
+        <v>-0.3206</v>
       </c>
       <c r="V7" t="n">
         <v>-4.1294</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0633</v>
+        <v>-1.0247</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1435</v>
+        <v>-0.92</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0803</v>
+        <v>-0.1047</v>
       </c>
       <c r="G8" t="n">
         <v>-1.351</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2877</v>
+        <v>0.3263</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5617</v>
+        <v>0.3767</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>V. ALVES BENITE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6119</v>
+        <v>-2.0597</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1624</v>
+        <v>-4.2182</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4495</v>
+        <v>2.1585</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8622</v>
+        <v>0.7568</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0892</v>
+        <v>-0.9094</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.773</v>
+        <v>1.6663</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.077</v>
+        <v>0.8073</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1918</v>
+        <v>-0.5562</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1147</v>
+        <v>1.3635</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7852</v>
+        <v>-0.0505</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8974</v>
+        <v>-0.3532</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8878</v>
+        <v>0.3028</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>-4.5676</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0773</v>
+        <v>-0.6414</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8292</v>
+        <v>-0.4578</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2481</v>
+        <v>-0.1836</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. ALVES BENITE</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7044</v>
+        <v>-3.0328</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6472</v>
+        <v>-1.4292</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9428</v>
+        <v>-1.6036</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7568</v>
+        <v>-3.8622</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9094</v>
+        <v>-2.0892</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6663</v>
+        <v>-1.773</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8073</v>
+        <v>-1.077</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5562</v>
+        <v>-1.1918</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3635</v>
+        <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0505</v>
+        <v>-2.7852</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3532</v>
+        <v>-0.8974</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3028</v>
+        <v>-1.8878</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.5676</v>
+        <v>-1.305</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2862</v>
+        <v>0.6564</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8868</v>
+        <v>0.5624</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3993</v>
+        <v>0.094</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3731</v>
+        <v>-4.0263</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0264</v>
+        <v>-2.8029</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3467</v>
+        <v>-1.2234</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7272</v>
@@ -1312,13 +1312,13 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5583</v>
+        <v>-0.2115</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3425</v>
+        <v>-0.119</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2158</v>
+        <v>-0.0925</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,34 +1345,34 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.125300000000001</v>
+        <v>-0.09799999999999986</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.249599999999999</v>
+        <v>-6.222200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>6.124499999999999</v>
+        <v>6.1244</v>
       </c>
       <c r="G12" t="n">
-        <v>6.9527</v>
+        <v>6.952700000000002</v>
       </c>
       <c r="H12" t="n">
         <v>2.159800000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>4.793099999999999</v>
+        <v>4.793100000000001</v>
       </c>
       <c r="J12" t="n">
         <v>9.806900000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8383</v>
+        <v>4.838300000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>4.968500000000001</v>
+        <v>4.9685</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.854200000000001</v>
+        <v>-2.8542</v>
       </c>
       <c r="N12" t="n">
         <v>-2.6786</v>
@@ -1381,7 +1381,7 @@
         <v>-0.1755999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-14.1378</v>
@@ -1390,16 +1390,16 @@
         <v>14.1379</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.8601</v>
+        <v>-1.8326</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6762</v>
+        <v>-0.6488</v>
       </c>
       <c r="U12" t="n">
         <v>-1.1838</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.2181</v>
+        <v>-5.218100000000001</v>
       </c>
       <c r="W12" t="n">
         <v>-1.2425</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3415</v>
+        <v>4.8912</v>
       </c>
       <c r="E13" t="n">
-        <v>1.421</v>
+        <v>2.3071</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9205</v>
+        <v>2.5842</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9782</v>
+        <v>2.042</v>
       </c>
       <c r="H13" t="n">
-        <v>2.132</v>
+        <v>1.6699</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1538</v>
+        <v>0.3721</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8898</v>
+        <v>2.2542</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9193</v>
+        <v>1.5242</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0295</v>
+        <v>0.73</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0883</v>
+        <v>-0.2121</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2127</v>
+        <v>0.1457</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1243</v>
+        <v>-0.3578</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>0.644</v>
+        <v>0.7171</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5312</v>
+        <v>0.0529</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1128</v>
+        <v>0.6642</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5443</v>
+        <v>0.1745</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5443</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2271</v>
+        <v>4.6934</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9718</v>
+        <v>1.1975</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2553</v>
+        <v>3.4959</v>
       </c>
       <c r="G14" t="n">
-        <v>2.042</v>
+        <v>0.9782</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6699</v>
+        <v>2.132</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3721</v>
+        <v>-1.1538</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2542</v>
+        <v>0.8898</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5242</v>
+        <v>1.9193</v>
       </c>
       <c r="L14" t="n">
-        <v>0.73</v>
+        <v>-1.0295</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2121</v>
+        <v>0.0883</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1457</v>
+        <v>0.2127</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3578</v>
+        <v>-0.1243</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>0.053</v>
+        <v>0.9959</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2824</v>
+        <v>0.3076</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3354</v>
+        <v>0.6883</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1745</v>
+        <v>0.5443</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1745</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1187</v>
+        <v>1.8555</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5251</v>
+        <v>-0.4133</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6438</v>
+        <v>2.2688</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7909</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3871</v>
+        <v>1.1239</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.1034</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3955</v>
+        <v>1.0205</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7666</v>
+        <v>1.267</v>
       </c>
       <c r="E16" t="n">
-        <v>1.825</v>
+        <v>-0.7725</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0584</v>
+        <v>2.0396</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3294</v>
+        <v>3.705</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4507</v>
+        <v>0.657</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7802</v>
+        <v>3.048</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9393</v>
+        <v>4.5801</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0836</v>
+        <v>1.1743</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1442</v>
+        <v>3.4058</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2688</v>
+        <v>-0.8751</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6328</v>
+        <v>-0.5173</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6359</v>
+        <v>-0.3578</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6525</v>
+        <v>-4.3501</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-6.5252</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.704</v>
+        <v>0.587</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8857</v>
+        <v>-0.1526</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1817</v>
+        <v>0.7396</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7395</v>
+        <v>1.3252</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2846</v>
+        <v>1.1462</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3619</v>
+        <v>1.2662</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9227</v>
+        <v>-0.1201</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.486</v>
+        <v>-0.3294</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0771</v>
+        <v>1.4507</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4089</v>
+        <v>-1.7802</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6842</v>
+        <v>0.9393</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.7607</v>
+        <v>2.0836</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0765</v>
+        <v>-1.1442</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8018</v>
+        <v>-1.2688</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3164</v>
+        <v>-0.6328</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4854</v>
+        <v>-0.6359</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2708</v>
+        <v>0.0835</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8736</v>
+        <v>0.3269</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3972</v>
+        <v>-0.2434</v>
       </c>
       <c r="V17" t="n">
-        <v>2.6297</v>
+        <v>0.7395</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3698</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3255</v>
+        <v>0.7952</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1078</v>
+        <v>0.0266</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4333</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>3.705</v>
+        <v>-3.486</v>
       </c>
       <c r="H18" t="n">
-        <v>0.657</v>
+        <v>-2.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>3.048</v>
+        <v>-1.4089</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5801</v>
+        <v>-1.6842</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1743</v>
+        <v>-1.7607</v>
       </c>
       <c r="L18" t="n">
-        <v>3.4058</v>
+        <v>0.0765</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8751</v>
+        <v>-1.8018</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5173</v>
+        <v>-0.3164</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3578</v>
+        <v>-1.4854</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.3501</v>
+        <v>0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>-6.5252</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3545</v>
+        <v>0.7814</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4879</v>
+        <v>0.5384</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1334</v>
+        <v>0.243</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3252</v>
+        <v>2.6297</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3252</v>
+        <v>2.2599</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1455</v>
+        <v>-0.2077</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9569</v>
+        <v>-1.2863</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8114</v>
+        <v>1.0786</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9481000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2621</v>
+        <v>0.6757</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4675</v>
+        <v>0.2031</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2054</v>
+        <v>0.4726</v>
       </c>
       <c r="V19" t="n">
         <v>0.9347</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4491</v>
+        <v>-1.9225</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7996</v>
+        <v>-1.5761</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6495</v>
+        <v>-0.3464</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0293</v>
@@ -2014,13 +2014,13 @@
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5498</v>
+        <v>-0.0231</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1334</v>
+        <v>0.0901</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4164</v>
+        <v>-0.1133</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6594</v>
+        <v>-2.5592</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0731</v>
+        <v>-2.8496</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4137</v>
+        <v>0.2904</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0409</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3358</v>
+        <v>-0.2355</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.4614</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3492</v>
+        <v>0.2259</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0109</v>
+        <v>-3.4772</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4432</v>
+        <v>-2.002</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5676</v>
+        <v>-1.4752</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3811</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3272</v>
+        <v>-0.1391</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7487</v>
+        <v>0.1899</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4214</v>
+        <v>-0.329</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7395</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6738</v>
+        <v>-3.8665</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7983</v>
+        <v>-2.0218</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8755</v>
+        <v>-1.8447</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6722</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0239</v>
+        <v>-0.2166</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2091</v>
+        <v>-0.0144</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.233</v>
+        <v>-0.2022</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.125300000000001</v>
+        <v>2.6154</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1243</v>
+        <v>-6.1242</v>
       </c>
       <c r="F24" t="n">
-        <v>7.2497</v>
+        <v>8.739700000000003</v>
       </c>
       <c r="G24" t="n">
         <v>-6.9527</v>
@@ -2299,7 +2299,7 @@
         <v>-4.793099999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>2.854200000000001</v>
+        <v>2.8542</v>
       </c>
       <c r="K24" t="n">
         <v>2.678500000000001</v>
@@ -2317,7 +2317,7 @@
         <v>-4.9686</v>
       </c>
       <c r="P24" t="n">
-        <v>9.999999999932285e-05</v>
+        <v>9.99999999995449e-05</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.1379</v>
@@ -2326,13 +2326,13 @@
         <v>14.1379</v>
       </c>
       <c r="S24" t="n">
-        <v>2.86</v>
+        <v>4.3502</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1837</v>
+        <v>1.1839</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6764</v>
+        <v>3.1662</v>
       </c>
       <c r="V24" t="n">
         <v>5.218000000000002</v>
